--- a/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
+++ b/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
@@ -2037,13 +2037,13 @@
     </row>
     <row r="2">
       <c r="A2" s="20" t="n">
-        <v>0.18</v>
+        <v>0.2437485685188716</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>260.7955492568087</v>
+        <v>211.95934597485</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>162.5650136542025</v>
+        <v>122.1265482723757</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2052,13 +2052,13 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
-        <v>0.22</v>
+        <v>0.2837485685188716</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>157.8113353291278</v>
+        <v>152.3943501597619</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>70.94989596030793</v>
+        <v>70.10034183574056</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2067,13 +2067,13 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
-        <v>0.26</v>
+        <v>0.3037485685188716</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>119.5972615823584</v>
+        <v>133.7027890895464</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>43.79251476003786</v>
+        <v>55.88696664744229</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
-        <v>0.3</v>
+        <v>0.3237485685188716</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>97.18780941172402</v>
+        <v>118.9724199380305</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>31.36864964212337</v>
+        <v>45.74742866171763</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
-        <v>0.3237</v>
+        <v>0.3437485685188716</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>87.53097227778994</v>
+        <v>107.0313026377783</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>27.02519646668626</v>
+        <v>38.35305553607058</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
-        <v>0.3579</v>
+        <v>0.3637485685188716</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>76.52073924326267</v>
+        <v>97.14815921409972</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>22.89072398023622</v>
+        <v>32.8732712141484</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="8">
       <c r="A8" s="20" t="n">
-        <v>0.4</v>
+        <v>0.4037485685188716</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>66.19076308220998</v>
+        <v>81.75426375262785</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>19.82924631124083</v>
+        <v>25.64354362310214</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>16.70687349288987</v>
+        <v>37.36344227330636</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>43.36179441121191</v>
+        <v>70.22115890128019</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>62.31330837739289</v>
+        <v>94.4729254177726</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>76.51111189991467</v>
+        <v>113.2392192375924</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>87.55363551231095</v>
+        <v>128.244470063715</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>103.6198531433314</v>
+        <v>150.7963229539649</v>
       </c>
     </row>
   </sheetData>
@@ -2560,7 +2560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>146021.8134787844</v>
+        <v>221705.727430978</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>184374.7879962359</v>
+        <v>244183.0425779828</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>76.51111189991467</v>
+        <v>113.2392192375924</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +2684,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>35522.11542829841</v>
+        <v>78802.21433028321</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>97053.80091853102</v>
+        <v>131255.351000734</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>22.8875007671344</v>
+        <v>43.89059158325536</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>168693.1832297173</v>
+        <v>233519.8692404983</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>202290.550844299</v>
+        <v>253519.0185352381</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>87.51313938795413</v>
+        <v>118.9724199380305</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +2732,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>44033.20019807658</v>
+        <v>82628.51271199735</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>103779.5778782064</v>
+        <v>134279.0348427699</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>27.01778445174855</v>
+        <v>45.74742866171763</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.2986554569408647</v>
+        <v>0.2905246324533263</v>
       </c>
     </row>
     <row r="16">
@@ -2788,17 +2788,27 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.2009562933062576</v>
+        <v>0.1656407888144581</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Discount rate this workbook uses</t>
+          <t>Cost of capital, first year</t>
         </is>
       </c>
       <c r="B17" s="13" t="n">
         <v>0.3579340986813324</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Cost of capital, once normalised</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0.2193244111908764</v>
       </c>
     </row>
   </sheetData>
@@ -2850,10 +2860,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>22.8875007671344</v>
+        <v>43.89059158325536</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>87.51313938795413</v>
+        <v>118.9724199380305</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -3153,7 +3163,7 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>0.15</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
@@ -3228,7 +3238,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>134161.2538555432</v>
+        <v>183703.1858848733</v>
       </c>
     </row>
     <row r="3">
@@ -3238,7 +3248,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>3892.961938842827</v>
+        <v>14029.00760827959</v>
       </c>
     </row>
     <row r="4">
@@ -3248,7 +3258,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>7967.597684398287</v>
+        <v>23973.53393782507</v>
       </c>
     </row>
     <row r="5">
@@ -3330,7 +3340,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-48940.92548254842</v>
+        <v>-64816.58485299512</v>
       </c>
     </row>
     <row r="13">
@@ -4331,7 +4341,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>3892.961938842827</v>
+        <v>14029.00760827959</v>
       </c>
     </row>
     <row r="14">
@@ -4341,7 +4351,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>7967.597684398287</v>
+        <v>23973.53393782507</v>
       </c>
     </row>
     <row r="15">

--- a/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
+++ b/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Slower conversion, EGP/share</t>
+          <t>Slower conversion, EGP/share (minority at value share, adopted)</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Faster conversion, EGP/share (minority at book)</t>
+          <t>Faster conversion, EGP/share (minority at value share, adopted)</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
@@ -2040,10 +2040,10 @@
         <v>0.2437485685188716</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>211.95934597485</v>
+        <v>196.5101788932792</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>122.1265482723757</v>
+        <v>125.5209481014641</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2055,10 +2055,10 @@
         <v>0.2837485685188716</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>152.3943501597619</v>
+        <v>149.4396952483696</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>70.10034183574056</v>
+        <v>84.40789729584293</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2070,10 +2070,10 @@
         <v>0.3037485685188716</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>133.7027890895464</v>
+        <v>134.6689258121608</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>55.88696664744229</v>
+        <v>73.17595754356496</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2085,10 +2085,10 @@
         <v>0.3237485685188716</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>118.9724199380305</v>
+        <v>123.028438127374</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>45.74742866171763</v>
+        <v>65.16331605181323</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2100,10 +2100,10 @@
         <v>0.3437485685188716</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>107.0313026377783</v>
+        <v>113.5921213965149</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>38.35305553607058</v>
+        <v>59.32000632749752</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2115,10 +2115,10 @@
         <v>0.3637485685188716</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>97.14815921409972</v>
+        <v>105.782092460582</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>32.8732712141484</v>
+        <v>54.98967616003811</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2130,10 +2130,10 @@
         <v>0.4037485685188716</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>81.75426375262785</v>
+        <v>93.61726151188044</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>25.64354362310214</v>
+        <v>49.27647548446123</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>37.36344227330636</v>
+        <v>58.53797697850982</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>70.22115890128019</v>
+        <v>84.50337145192553</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>94.4729254177726</v>
+        <v>103.6680228307067</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>113.2392192375924</v>
+        <v>118.4978488759164</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>128.244470063715</v>
+        <v>130.3555583231125</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>150.7963229539649</v>
+        <v>148.1768744855158</v>
       </c>
     </row>
   </sheetData>
@@ -2398,11 +2398,11 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>11.53</v>
+        <v>13.7</v>
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
@@ -2418,11 +2418,11 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>27.48</v>
+        <v>31.01</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -2478,11 +2478,11 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>40.16</v>
+        <v>41.5</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.2905246324533263</v>
+        <v>0.3187056809350682</v>
       </c>
     </row>
     <row r="16">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.1656407888144581</v>
+        <v>0.1744219434346233</v>
       </c>
     </row>
     <row r="17">

--- a/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
+++ b/engine/publish_queue/TMGH/TMGH_Valuation_Model_02092026.xlsx
@@ -2037,13 +2037,13 @@
     </row>
     <row r="2">
       <c r="A2" s="20" t="n">
-        <v>0.2437485685188716</v>
+        <v>0.2433591860944612</v>
       </c>
       <c r="B2" s="9" t="n">
-        <v>196.5101788932792</v>
+        <v>197.0370228802018</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>125.5209481014641</v>
+        <v>126.0026582327154</v>
       </c>
       <c r="D2" s="10">
         <f>B2/'Summary'!$B$2-1</f>
@@ -2052,13 +2052,13 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="n">
-        <v>0.2837485685188716</v>
+        <v>0.2833591860944613</v>
       </c>
       <c r="B3" s="9" t="n">
-        <v>149.4396952483696</v>
+        <v>149.7078407339783</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>84.40789729584293</v>
+        <v>84.61493533824613</v>
       </c>
       <c r="D3" s="10">
         <f>B3/'Summary'!$B$2-1</f>
@@ -2067,13 +2067,13 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="n">
-        <v>0.3037485685188716</v>
+        <v>0.3033591860944612</v>
       </c>
       <c r="B4" s="9" t="n">
-        <v>134.6689258121608</v>
+        <v>134.8779631426536</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>73.17595754356496</v>
+        <v>73.322000779918</v>
       </c>
       <c r="D4" s="10">
         <f>B4/'Summary'!$B$2-1</f>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="5">
       <c r="A5" s="20" t="n">
-        <v>0.3237485685188716</v>
+        <v>0.3233591860944612</v>
       </c>
       <c r="B5" s="9" t="n">
-        <v>123.028438127374</v>
+        <v>123.1967553373328</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>65.16331605181323</v>
+        <v>65.26903261982723</v>
       </c>
       <c r="D5" s="10">
         <f>B5/'Summary'!$B$2-1</f>
@@ -2097,13 +2097,13 @@
     </row>
     <row r="6">
       <c r="A6" s="20" t="n">
-        <v>0.3437485685188716</v>
+        <v>0.3433591860944613</v>
       </c>
       <c r="B6" s="9" t="n">
-        <v>113.5921213965149</v>
+        <v>113.7308299366004</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>59.32000632749752</v>
+        <v>59.39795607481796</v>
       </c>
       <c r="D6" s="10">
         <f>B6/'Summary'!$B$2-1</f>
@@ -2112,13 +2112,13 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="n">
-        <v>0.3637485685188716</v>
+        <v>0.3633591860944612</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>105.782092460582</v>
+        <v>105.8984267910268</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>54.98967616003811</v>
+        <v>55.04797094819054</v>
       </c>
       <c r="D7" s="10">
         <f>B7/'Summary'!$B$2-1</f>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="8">
       <c r="A8" s="20" t="n">
-        <v>0.4037485685188716</v>
+        <v>0.4033591860944613</v>
       </c>
       <c r="B8" s="9" t="n">
-        <v>93.61726151188044</v>
+        <v>93.7023601270504</v>
       </c>
       <c r="C8" s="9" t="n">
-        <v>49.27647548446123</v>
+        <v>49.31017509612661</v>
       </c>
       <c r="D8" s="10">
         <f>B8/'Summary'!$B$2-1</f>
@@ -2157,7 +2157,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="9" t="n">
-        <v>58.53797697850982</v>
+        <v>58.64158059455131</v>
       </c>
     </row>
     <row r="12">
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="B12" s="9" t="n">
-        <v>84.50337145192553</v>
+        <v>84.63726479471869</v>
       </c>
     </row>
     <row r="13">
@@ -2173,7 +2173,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="9" t="n">
-        <v>103.6680228307067</v>
+        <v>103.8263898538421</v>
       </c>
     </row>
     <row r="14">
@@ -2181,7 +2181,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="9" t="n">
-        <v>118.4978488759164</v>
+        <v>118.6766355213929</v>
       </c>
     </row>
     <row r="15">
@@ -2189,7 +2189,7 @@
         <v>16</v>
       </c>
       <c r="B15" s="9" t="n">
-        <v>130.3555583231125</v>
+        <v>130.5517255732667</v>
       </c>
     </row>
     <row r="16">
@@ -2197,7 +2197,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="9" t="n">
-        <v>148.1768744855158</v>
+        <v>148.4011061241003</v>
       </c>
     </row>
   </sheetData>
@@ -2295,7 +2295,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.3714622808056017</v>
+        <v>0.3710320302096666</v>
       </c>
     </row>
     <row r="8">
@@ -2305,7 +2305,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.3343918983056465</v>
+        <v>0.3341014637211595</v>
       </c>
     </row>
     <row r="9">
@@ -2592,11 +2592,11 @@
         </is>
       </c>
       <c r="B2" s="5" t="n">
-        <v>97.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Egyptian Exchange close, 23 August 2026, from the same cleaned price history the probability distribution is fitted to</t>
+          <t>Egyptian Exchange close for 2 September 2026, the latest price this repository holds for this name, read from the committed supplied price file through gap_today.latest_price_per_ticker(). SUPERSEDES the 23 August 2026 close of 97.80 the study was struck at: a fair value put against a price ten days old is a comparison a reader cannot use, however good the fair value is.</t>
         </is>
       </c>
     </row>
@@ -2660,17 +2660,17 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>221705.727430978</v>
+        <v>222171.938483465</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>244183.0425779828</v>
+        <v>244551.4599583733</v>
       </c>
       <c r="D7" s="9">
         <f>C7/$B$3</f>
         <v/>
       </c>
       <c r="E7" s="9" t="n">
-        <v>113.2392192375924</v>
+        <v>113.4654634773997</v>
       </c>
       <c r="F7" s="10">
         <f>D7/$B$2-1</f>
@@ -2684,17 +2684,17 @@
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>78802.21433028321</v>
+        <v>79079.60237675605</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>131255.351000734</v>
+        <v>131474.5533917713</v>
       </c>
       <c r="D8" s="9">
         <f>C8/$B$3</f>
         <v/>
       </c>
       <c r="E8" s="9" t="n">
-        <v>43.89059158325536</v>
+        <v>44.02520325187862</v>
       </c>
       <c r="F8" s="10">
         <f>D8/$B$2-1</f>
@@ -2708,17 +2708,17 @@
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>233519.8692404983</v>
+        <v>233958.7797832709</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>253519.0185352381</v>
+        <v>253865.8620335452</v>
       </c>
       <c r="D9" s="9">
         <f>C9/$B$3</f>
         <v/>
       </c>
       <c r="E9" s="9" t="n">
-        <v>118.9724199380305</v>
+        <v>119.1854157080004</v>
       </c>
       <c r="F9" s="10">
         <f>D9/$B$2-1</f>
@@ -2732,17 +2732,17 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>82628.51271199735</v>
+        <v>82904.18337133406</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>134279.0348427699</v>
+        <v>134496.8800903709</v>
       </c>
       <c r="D10" s="9">
         <f>C10/$B$3</f>
         <v/>
       </c>
       <c r="E10" s="9" t="n">
-        <v>45.74742866171763</v>
+        <v>45.88120691177434</v>
       </c>
       <c r="F10" s="10">
         <f>D10/$B$2-1</f>
@@ -2778,7 +2778,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>0.3187056809350682</v>
+        <v>0.3231986232272755</v>
       </c>
     </row>
     <row r="16">
@@ -2788,7 +2788,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>0.1744219434346233</v>
+        <v>0.1757914038035151</v>
       </c>
     </row>
     <row r="17">
@@ -2798,7 +2798,7 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>0.3579340986813324</v>
+        <v>0.3573828894703562</v>
       </c>
     </row>
     <row r="18">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>0.2193244111908764</v>
+        <v>0.2190258178466077</v>
       </c>
     </row>
   </sheetData>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>43.89059158325536</v>
+        <v>44.02520325187862</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>118.9724199380305</v>
+        <v>119.1854157080004</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
@@ -2878,10 +2878,10 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>3.326271266868016</v>
+        <v>3.33274603069955</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>12.63251646941587</v>
+        <v>12.64818881769384</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
@@ -2896,10 +2896,10 @@
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>15.44112968405148</v>
+        <v>15.46564175092172</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>23.76576967997966</v>
+        <v>23.80326205675117</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B2" s="7" t="n">
-        <v>183703.1858848733</v>
+        <v>183998.5351018925</v>
       </c>
     </row>
     <row r="3">
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="B3" s="7" t="n">
-        <v>14029.00760827959</v>
+        <v>14084.37260100699</v>
       </c>
     </row>
     <row r="4">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>23973.53393782507</v>
+        <v>24089.03078056552</v>
       </c>
     </row>
     <row r="5">
@@ -3340,7 +3340,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>-64816.58485299512</v>
+        <v>-64914.37852509163</v>
       </c>
     </row>
     <row r="13">
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>14029.00760827959</v>
+        <v>14084.37260100699</v>
       </c>
     </row>
     <row r="14">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>23973.53393782507</v>
+        <v>24089.03078056552</v>
       </c>
     </row>
     <row r="15">
